--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T14:55:17+00:00</t>
+    <t>2023-12-11T15:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Observation du niveau de douleur</t>
+    <t>Profil de la ressource Observation pour définir un niveau de douleur</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:07:49+00:00</t>
+    <t>2023-12-11T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:09:19+00:00</t>
+    <t>2023-12-11T15:13:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:13:34+00:00</t>
+    <t>2023-12-11T15:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:58:18+00:00</t>
+    <t>2023-12-11T16:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T16:02:47+00:00</t>
+    <t>2023-12-11T17:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T17:03:26+00:00</t>
+    <t>2023-12-12T13:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T13:44:55+00:00</t>
+    <t>2023-12-12T13:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$96</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3534" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3726" uniqueCount="656">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T13:59:44+00:00</t>
+    <t>2023-12-12T14:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1098,14 +1098,6 @@
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="72514-3"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
@@ -1128,6 +1120,34 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>value:code}
+value:system}</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:painServerCode</t>
+  </si>
+  <si>
+    <t>painServerCode</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="72514-3"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -2363,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP91"/>
+  <dimension ref="A1:AP96"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
@@ -6921,7 +6941,7 @@
         <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>82</v>
@@ -6939,10 +6959,10 @@
         <v>153</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6975,30 +6995,30 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>356</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7006,35 +7026,31 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>358</v>
+        <v>109</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>359</v>
+        <v>110</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7082,7 +7098,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>357</v>
+        <v>112</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7091,25 +7107,25 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>365</v>
+        <v>113</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -7117,14 +7133,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7140,19 +7156,19 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>368</v>
+        <v>116</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>369</v>
+        <v>117</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>370</v>
+        <v>118</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>371</v>
+        <v>119</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7190,19 +7206,19 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>367</v>
+        <v>123</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7214,7 +7230,7 @@
         <v>105</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7223,13 +7239,13 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>372</v>
+        <v>107</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -7237,21 +7253,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7263,19 +7279,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>375</v>
+        <v>149</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>376</v>
+        <v>276</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>377</v>
+        <v>277</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>378</v>
+        <v>278</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>379</v>
+        <v>279</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7312,46 +7328,44 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>280</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>281</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>382</v>
+        <v>282</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -7359,14 +7373,16 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D42" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7376,7 +7392,7 @@
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7385,19 +7401,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>386</v>
+        <v>149</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>387</v>
+        <v>276</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>388</v>
+        <v>277</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>389</v>
+        <v>278</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>390</v>
+        <v>279</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7407,7 +7423,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7446,34 +7462,34 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>391</v>
+        <v>105</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>392</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>394</v>
+        <v>281</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>395</v>
+        <v>282</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7481,10 +7497,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7507,18 +7523,20 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>398</v>
+        <v>335</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>399</v>
+        <v>336</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7566,7 +7584,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7587,13 +7605,13 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>401</v>
+        <v>340</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -7601,10 +7619,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7612,13 +7630,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7627,19 +7645,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>228</v>
+        <v>368</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7688,13 +7706,13 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>105</v>
@@ -7703,19 +7721,19 @@
         <v>230</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>409</v>
+        <v>370</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>410</v>
+        <v>371</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>411</v>
+        <v>372</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>412</v>
+        <v>373</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7723,10 +7741,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7737,10 +7755,10 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7749,20 +7767,18 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>414</v>
+        <v>375</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>415</v>
+        <v>376</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7810,49 +7826,49 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>418</v>
+        <v>105</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>420</v>
+        <v>352</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>421</v>
+        <v>379</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7868,19 +7884,23 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>109</v>
+        <v>382</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>110</v>
+        <v>383</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7928,7 +7948,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>112</v>
+        <v>380</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7937,25 +7957,25 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>113</v>
+        <v>389</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7963,44 +7983,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>115</v>
+        <v>392</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>116</v>
+        <v>393</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>117</v>
+        <v>394</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>118</v>
+        <v>395</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8036,46 +8058,46 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>123</v>
+        <v>391</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>105</v>
+        <v>398</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>124</v>
+        <v>399</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>107</v>
+        <v>402</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -8083,10 +8105,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8109,20 +8131,18 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>426</v>
+        <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8170,7 +8190,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>404</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8191,13 +8211,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8205,10 +8225,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8219,38 +8239,36 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>412</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>309</v>
+        <v>228</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q49" t="s" s="2">
-        <v>438</v>
-      </c>
+      <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8270,13 +8288,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8294,34 +8312,34 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8329,10 +8347,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8340,13 +8358,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8355,19 +8373,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>109</v>
+        <v>421</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>309</v>
+        <v>423</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8377,7 +8395,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8416,7 +8434,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8425,7 +8443,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>105</v>
+        <v>425</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8434,27 +8452,27 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8474,23 +8492,19 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>453</v>
+        <v>110</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8499,7 +8513,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8538,7 +8552,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>112</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8547,10 +8561,10 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8559,10 +8573,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>460</v>
+        <v>113</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8573,21 +8587,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8596,23 +8610,21 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>117</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>118</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8621,7 +8633,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>82</v>
@@ -8648,31 +8660,31 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>466</v>
+        <v>123</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8681,10 +8693,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>467</v>
+        <v>107</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8695,10 +8707,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8712,28 +8724,28 @@
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>257</v>
+        <v>433</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>434</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>472</v>
+        <v>437</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8758,13 +8770,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8782,7 +8794,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8791,7 +8803,7 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8803,10 +8815,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>107</v>
+        <v>439</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8817,10 +8829,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8837,26 +8849,32 @@
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>110</v>
+        <v>442</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="R54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8876,13 +8894,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8900,7 +8918,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>112</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8909,10 +8927,10 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8921,10 +8939,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>113</v>
+        <v>450</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8935,21 +8953,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8958,21 +8976,23 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>117</v>
+        <v>452</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>118</v>
+        <v>453</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8981,7 +9001,7 @@
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -9008,31 +9028,31 @@
         <v>82</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>123</v>
+        <v>456</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -9041,10 +9061,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9055,10 +9075,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9069,7 +9089,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -9081,19 +9101,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>276</v>
+        <v>460</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>277</v>
+        <v>461</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>278</v>
+        <v>462</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>279</v>
+        <v>463</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9103,7 +9123,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9142,16 +9162,16 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>280</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>105</v>
+        <v>466</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9163,10 +9183,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>281</v>
+        <v>457</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>282</v>
+        <v>467</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9177,10 +9197,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9188,7 +9208,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
@@ -9200,19 +9220,23 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>110</v>
+        <v>469</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9221,7 +9245,7 @@
         <v>82</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>82</v>
@@ -9260,7 +9284,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>112</v>
+        <v>473</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9269,10 +9293,10 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9281,10 +9305,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>113</v>
+        <v>474</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9295,24 +9319,24 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9321,18 +9345,20 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>117</v>
+        <v>476</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>118</v>
+        <v>477</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9356,43 +9382,43 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>123</v>
+        <v>475</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>105</v>
+        <v>482</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9401,10 +9427,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>107</v>
+        <v>483</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9415,10 +9441,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9426,7 +9452,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>93</v>
@@ -9438,23 +9464,19 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9502,7 +9524,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>294</v>
+        <v>112</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9511,10 +9533,10 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9523,10 +9545,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>296</v>
+        <v>113</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9537,21 +9559,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9560,19 +9582,19 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>299</v>
+        <v>117</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>300</v>
+        <v>118</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>301</v>
+        <v>119</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9610,31 +9632,31 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>302</v>
+        <v>123</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9643,10 +9665,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>304</v>
+        <v>107</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9657,10 +9679,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9668,10 +9690,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9683,19 +9705,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9744,13 +9766,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>105</v>
@@ -9765,10 +9787,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9779,10 +9801,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9802,23 +9824,19 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>317</v>
+        <v>110</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9866,7 +9884,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>320</v>
+        <v>112</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9875,10 +9893,10 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9887,10 +9905,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>322</v>
+        <v>113</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9901,21 +9919,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9924,23 +9942,21 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>325</v>
+        <v>116</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>326</v>
+        <v>117</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>327</v>
+        <v>118</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9976,31 +9992,31 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>330</v>
+        <v>123</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10009,10 +10025,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>332</v>
+        <v>107</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10023,10 +10039,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10034,7 +10050,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
@@ -10049,19 +10065,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>338</v>
+        <v>292</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10110,7 +10126,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>339</v>
+        <v>294</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10131,10 +10147,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>340</v>
+        <v>295</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10145,21 +10161,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10168,23 +10184,21 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>490</v>
+        <v>299</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>491</v>
+        <v>300</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10208,13 +10222,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10232,13 +10246,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>488</v>
+        <v>302</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>105</v>
@@ -10250,27 +10264,27 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>497</v>
+        <v>303</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>498</v>
+        <v>304</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10278,10 +10292,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10290,22 +10304,22 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>501</v>
+        <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>502</v>
+        <v>307</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>503</v>
+        <v>308</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>504</v>
+        <v>309</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>505</v>
+        <v>310</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10354,13 +10368,13 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>500</v>
+        <v>312</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>105</v>
@@ -10375,10 +10389,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>506</v>
+        <v>313</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>507</v>
+        <v>314</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10389,10 +10403,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10412,21 +10426,23 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>509</v>
+        <v>317</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10450,13 +10466,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10474,7 +10490,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>508</v>
+        <v>320</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10492,27 +10508,27 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>515</v>
+        <v>321</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>516</v>
+        <v>322</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10526,28 +10542,28 @@
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K68" t="s" s="2">
-        <v>257</v>
+        <v>325</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>519</v>
+        <v>326</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>520</v>
+        <v>327</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>521</v>
+        <v>328</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>522</v>
+        <v>329</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10572,11 +10588,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10594,7 +10612,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>518</v>
+        <v>330</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10615,10 +10633,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>524</v>
+        <v>331</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>525</v>
+        <v>332</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10629,10 +10647,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10652,21 +10670,23 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>527</v>
+        <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>528</v>
+        <v>335</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>529</v>
+        <v>336</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10714,7 +10734,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>526</v>
+        <v>339</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10726,44 +10746,44 @@
         <v>105</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>532</v>
+        <v>340</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>533</v>
+        <v>341</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>535</v>
+        <v>495</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>535</v>
+        <v>495</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10775,18 +10795,20 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>536</v>
+        <v>257</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>537</v>
+        <v>497</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>538</v>
+        <v>498</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10810,13 +10832,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10834,45 +10856,45 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>535</v>
+        <v>495</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>541</v>
+        <v>504</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>542</v>
+        <v>505</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>543</v>
+        <v>506</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10895,19 +10917,19 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>545</v>
+        <v>508</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>547</v>
+        <v>510</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>548</v>
+        <v>511</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>549</v>
+        <v>512</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10956,7 +10978,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10968,7 +10990,7 @@
         <v>105</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>550</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10977,10 +10999,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>552</v>
+        <v>514</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10991,10 +11013,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>553</v>
+        <v>515</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>553</v>
+        <v>515</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11017,15 +11039,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>109</v>
+        <v>257</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>110</v>
+        <v>516</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11050,13 +11074,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11074,7 +11098,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>112</v>
+        <v>515</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11083,50 +11107,50 @@
         <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>113</v>
+        <v>523</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>554</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>554</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -11135,18 +11159,20 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>117</v>
+        <v>526</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>118</v>
+        <v>527</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11170,43 +11196,41 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>123</v>
+        <v>525</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11215,10 +11239,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>107</v>
+        <v>532</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11229,46 +11253,44 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>116</v>
+        <v>534</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11316,45 +11338,45 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>107</v>
+        <v>540</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11377,16 +11399,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11436,7 +11458,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11445,36 +11467,36 @@
         <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>565</v>
+        <v>105</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>566</v>
+        <v>230</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>567</v>
+        <v>548</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11485,7 +11507,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11497,18 +11519,20 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11556,19 +11580,19 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>565</v>
+        <v>105</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11577,10 +11601,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11591,10 +11615,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11617,20 +11641,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>574</v>
+        <v>110</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11654,13 +11674,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11678,7 +11698,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>573</v>
+        <v>112</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11687,22 +11707,22 @@
         <v>93</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>581</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>498</v>
+        <v>113</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11713,14 +11733,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11739,20 +11759,18 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>257</v>
+        <v>116</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>583</v>
+        <v>117</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>584</v>
+        <v>118</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11776,31 +11794,31 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>588</v>
+        <v>82</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>582</v>
+        <v>123</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11812,19 +11830,19 @@
         <v>105</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>581</v>
+        <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>498</v>
+        <v>107</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11835,45 +11853,45 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>589</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>589</v>
+        <v>562</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>563</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>590</v>
+        <v>116</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>593</v>
+        <v>119</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>594</v>
+        <v>212</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11922,19 +11940,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>589</v>
+        <v>566</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>595</v>
+        <v>124</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11943,10 +11961,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>597</v>
+        <v>107</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11957,10 +11975,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11983,16 +12001,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>109</v>
+        <v>568</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>599</v>
+        <v>569</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>309</v>
+        <v>571</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12042,7 +12060,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12051,10 +12069,10 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>105</v>
+        <v>572</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>106</v>
+        <v>573</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12063,10 +12081,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>601</v>
+        <v>575</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12077,10 +12095,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>602</v>
+        <v>576</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>602</v>
+        <v>576</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12091,7 +12109,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12100,19 +12118,19 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>603</v>
+        <v>568</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>604</v>
+        <v>577</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>605</v>
+        <v>578</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>606</v>
+        <v>571</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12162,19 +12180,19 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>602</v>
+        <v>576</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>105</v>
+        <v>572</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>230</v>
+        <v>573</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12183,10 +12201,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>607</v>
+        <v>574</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>608</v>
+        <v>579</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12197,10 +12215,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12211,7 +12229,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12220,21 +12238,23 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>610</v>
+        <v>257</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>611</v>
+        <v>581</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>612</v>
+        <v>582</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12258,13 +12278,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>585</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12282,31 +12302,31 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>614</v>
+        <v>505</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12317,10 +12337,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12334,28 +12354,28 @@
         <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>545</v>
+        <v>257</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>616</v>
+        <v>590</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12380,13 +12400,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12404,7 +12424,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12416,19 +12436,19 @@
         <v>105</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>619</v>
+        <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>620</v>
+        <v>588</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>621</v>
+        <v>505</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12439,10 +12459,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12465,16 +12485,20 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>109</v>
+        <v>597</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>110</v>
+        <v>598</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12522,7 +12546,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>112</v>
+        <v>596</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12531,10 +12555,10 @@
         <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>82</v>
+        <v>602</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12543,10 +12567,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>82</v>
+        <v>603</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>113</v>
+        <v>604</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12557,21 +12581,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12583,16 +12607,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>117</v>
+        <v>606</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>118</v>
+        <v>607</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>119</v>
+        <v>309</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12630,31 +12654,31 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>123</v>
+        <v>605</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12663,10 +12687,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>107</v>
+        <v>608</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12677,14 +12701,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12697,26 +12721,24 @@
         <v>82</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>116</v>
+        <v>610</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>558</v>
+        <v>612</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12764,7 +12786,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>559</v>
+        <v>609</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12776,7 +12798,7 @@
         <v>105</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12785,10 +12807,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>107</v>
+        <v>615</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12799,10 +12821,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12810,13 +12832,13 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>82</v>
@@ -12825,20 +12847,18 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>257</v>
+        <v>617</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>629</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12862,13 +12882,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12886,34 +12906,34 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>630</v>
+        <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>353</v>
+        <v>614</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>354</v>
+        <v>621</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -12921,10 +12941,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12935,7 +12955,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>94</v>
@@ -12947,19 +12967,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>632</v>
+        <v>552</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>417</v>
+        <v>625</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12984,13 +13004,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>636</v>
+        <v>82</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -13008,45 +13028,45 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>638</v>
+        <v>105</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>106</v>
+        <v>626</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>639</v>
+        <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>420</v>
+        <v>627</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>421</v>
+        <v>628</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13060,7 +13080,7 @@
         <v>93</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>82</v>
@@ -13069,20 +13089,16 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>641</v>
+        <v>110</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13106,13 +13122,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13130,7 +13146,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>640</v>
+        <v>112</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13139,10 +13155,10 @@
         <v>93</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13151,10 +13167,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>476</v>
+        <v>113</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13165,14 +13181,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>645</v>
+        <v>630</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>645</v>
+        <v>630</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>489</v>
+        <v>115</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13191,20 +13207,18 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>257</v>
+        <v>116</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>490</v>
+        <v>117</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>491</v>
+        <v>118</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13228,31 +13242,31 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>645</v>
+        <v>123</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13264,37 +13278,37 @@
         <v>105</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>498</v>
+        <v>107</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>82</v>
+        <v>563</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13307,25 +13321,25 @@
         <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>647</v>
+        <v>564</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>648</v>
+        <v>565</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>548</v>
+        <v>119</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>549</v>
+        <v>212</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13374,7 +13388,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>646</v>
+        <v>566</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13383,10 +13397,10 @@
         <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13395,20 +13409,630 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>552</v>
+        <v>107</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP91">
+  <autoFilter ref="A1:AP96">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13418,7 +14042,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI90">
+  <conditionalFormatting sqref="A2:AI95">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T14:34:19+00:00</t>
+    <t>2023-12-12T16:43:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T16:43:39+00:00</t>
+    <t>2023-12-13T09:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
